--- a/base_backoffice.xlsx
+++ b/base_backoffice.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="MVLEbt9bej18V2j9riGCauZkGGjQ013ENnZhrLuGlXo="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Znk0HmE6canBtG9VRSo5I523/d94sfmHi8N3K6YxTPg="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="126">
   <si>
     <t>RELATÓRIO BACKOFFICE</t>
   </si>
@@ -283,6 +283,15 @@
     <t xml:space="preserve">Larissa </t>
   </si>
   <si>
+    <t>A partir de  13/07/2026</t>
+  </si>
+  <si>
+    <t>TATIANE SANTOS DE SOUZA (202587)</t>
+  </si>
+  <si>
+    <t>Tatiane</t>
+  </si>
+  <si>
     <t xml:space="preserve">1% e lançar o valor cheio </t>
   </si>
   <si>
@@ -368,6 +377,24 @@
   </si>
   <si>
     <t>A partir de 21/07/2026</t>
+  </si>
+  <si>
+    <t>BACKOFFICE - RIO WJ</t>
+  </si>
+  <si>
+    <t>214876 - ANA FLÁVIA MACHADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ana Flávia </t>
+  </si>
+  <si>
+    <t>A partir de 03/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215492 - GEOVANE GOUVEA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geovane </t>
   </si>
 </sst>
 </file>
@@ -3146,16 +3173,19 @@
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="1"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="19" t="s">
+      <c r="B69" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="D69" s="2"/>
-      <c r="E69" s="34">
-        <v>937.68</v>
+      <c r="C69" s="23" t="s">
+        <v>89</v>
       </c>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
+      <c r="D69" s="59"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="30"/>
+      <c r="G69" s="58" t="s">
+        <v>90</v>
+      </c>
+      <c r="H69" s="39"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
@@ -3178,12 +3208,15 @@
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="1"/>
       <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
+      <c r="C70" s="19" t="s">
+        <v>91</v>
+      </c>
       <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
+      <c r="E70" s="34">
+        <v>937.68</v>
+      </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
@@ -3205,15 +3238,13 @@
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="1"/>
-      <c r="B71" s="50" t="s">
-        <v>89</v>
-      </c>
+      <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
-      <c r="F71" s="6"/>
+      <c r="F71" s="2"/>
       <c r="G71" s="2"/>
-      <c r="H71" s="12"/>
+      <c r="H71" s="2"/>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
@@ -3235,19 +3266,15 @@
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="1"/>
-      <c r="B72" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="C72" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="D72" s="43"/>
-      <c r="E72" s="57"/>
-      <c r="F72" s="30"/>
-      <c r="G72" s="58" t="s">
+      <c r="B72" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="H72" s="39"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="12"/>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
@@ -3269,19 +3296,19 @@
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="1"/>
-      <c r="B73" s="12"/>
-      <c r="C73" s="23" t="s">
+      <c r="B73" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D73" s="2"/>
-      <c r="E73" s="12"/>
+      <c r="C73" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D73" s="43"/>
+      <c r="E73" s="57"/>
       <c r="F73" s="30"/>
       <c r="G73" s="58" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
-      <c r="H73" s="39">
-        <v>27.64</v>
-      </c>
+      <c r="H73" s="39"/>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
@@ -3301,19 +3328,21 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74" ht="17.25" customHeight="1">
+    <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="1"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="19" t="s">
-        <v>88</v>
+      <c r="B74" s="12"/>
+      <c r="C74" s="23" t="s">
+        <v>96</v>
       </c>
       <c r="D74" s="2"/>
-      <c r="E74" s="60">
+      <c r="E74" s="12"/>
+      <c r="F74" s="30"/>
+      <c r="G74" s="58" t="s">
+        <v>97</v>
+      </c>
+      <c r="H74" s="39">
         <v>27.64</v>
       </c>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
@@ -3333,81 +3362,77 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
     </row>
-    <row r="75" ht="14.25" customHeight="1">
-      <c r="A75" s="61"/>
-      <c r="B75" s="61"/>
-      <c r="C75" s="61"/>
-      <c r="D75" s="61"/>
-      <c r="E75" s="61"/>
-      <c r="F75" s="61"/>
-      <c r="G75" s="61"/>
-      <c r="H75" s="61"/>
-      <c r="I75" s="61"/>
-      <c r="J75" s="61"/>
-      <c r="K75" s="61"/>
-      <c r="L75" s="61"/>
-      <c r="M75" s="61"/>
-      <c r="N75" s="61"/>
-      <c r="O75" s="61"/>
-      <c r="P75" s="61"/>
-      <c r="Q75" s="61"/>
-      <c r="R75" s="61"/>
-      <c r="S75" s="61"/>
-      <c r="T75" s="61"/>
-      <c r="U75" s="61"/>
-      <c r="V75" s="61"/>
-      <c r="W75" s="61"/>
-      <c r="X75" s="61"/>
-      <c r="Y75" s="61"/>
-      <c r="Z75" s="61"/>
+    <row r="75" ht="17.25" customHeight="1">
+      <c r="A75" s="1"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D75" s="2"/>
+      <c r="E75" s="60">
+        <v>27.64</v>
+      </c>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1"/>
+      <c r="N75" s="1"/>
+      <c r="O75" s="1"/>
+      <c r="P75" s="1"/>
+      <c r="Q75" s="1"/>
+      <c r="R75" s="1"/>
+      <c r="S75" s="1"/>
+      <c r="T75" s="1"/>
+      <c r="U75" s="1"/>
+      <c r="V75" s="1"/>
+      <c r="W75" s="1"/>
+      <c r="X75" s="1"/>
+      <c r="Y75" s="1"/>
+      <c r="Z75" s="1"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
-      <c r="A76" s="1"/>
-      <c r="B76" s="62" t="s">
-        <v>95</v>
-      </c>
+      <c r="A76" s="61"/>
+      <c r="B76" s="61"/>
       <c r="C76" s="61"/>
       <c r="D76" s="61"/>
       <c r="E76" s="61"/>
-      <c r="F76" s="63"/>
+      <c r="F76" s="61"/>
       <c r="G76" s="61"/>
       <c r="H76" s="61"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="1"/>
-      <c r="K76" s="1"/>
-      <c r="L76" s="1"/>
-      <c r="M76" s="1"/>
-      <c r="N76" s="1"/>
-      <c r="O76" s="1"/>
-      <c r="P76" s="1"/>
-      <c r="Q76" s="1"/>
-      <c r="R76" s="1"/>
-      <c r="S76" s="1"/>
-      <c r="T76" s="1"/>
-      <c r="U76" s="1"/>
-      <c r="V76" s="1"/>
-      <c r="W76" s="1"/>
-      <c r="X76" s="1"/>
-      <c r="Y76" s="1"/>
-      <c r="Z76" s="1"/>
+      <c r="I76" s="61"/>
+      <c r="J76" s="61"/>
+      <c r="K76" s="61"/>
+      <c r="L76" s="61"/>
+      <c r="M76" s="61"/>
+      <c r="N76" s="61"/>
+      <c r="O76" s="61"/>
+      <c r="P76" s="61"/>
+      <c r="Q76" s="61"/>
+      <c r="R76" s="61"/>
+      <c r="S76" s="61"/>
+      <c r="T76" s="61"/>
+      <c r="U76" s="61"/>
+      <c r="V76" s="61"/>
+      <c r="W76" s="61"/>
+      <c r="X76" s="61"/>
+      <c r="Y76" s="61"/>
+      <c r="Z76" s="61"/>
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="1"/>
-      <c r="B77" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="C77" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="D77" s="65"/>
-      <c r="E77" s="65"/>
-      <c r="F77" s="66"/>
-      <c r="G77" s="67" t="s">
+      <c r="B77" s="62" t="s">
         <v>98</v>
       </c>
-      <c r="H77" s="39">
-        <v>225.07</v>
-      </c>
+      <c r="C77" s="61"/>
+      <c r="D77" s="61"/>
+      <c r="E77" s="61"/>
+      <c r="F77" s="63"/>
+      <c r="G77" s="61"/>
+      <c r="H77" s="61"/>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
@@ -3429,15 +3454,17 @@
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="1"/>
-      <c r="B78" s="61"/>
-      <c r="C78" s="64" t="s">
+      <c r="B78" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="D78" s="61"/>
-      <c r="E78" s="61"/>
+      <c r="C78" s="64" t="s">
+        <v>100</v>
+      </c>
+      <c r="D78" s="65"/>
+      <c r="E78" s="65"/>
       <c r="F78" s="66"/>
       <c r="G78" s="67" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H78" s="39">
         <v>225.07</v>
@@ -3464,14 +3491,18 @@
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="1"/>
       <c r="B79" s="61"/>
-      <c r="C79" s="19" t="s">
-        <v>88</v>
+      <c r="C79" s="64" t="s">
+        <v>102</v>
       </c>
       <c r="D79" s="61"/>
-      <c r="E79" s="60"/>
-      <c r="F79" s="61"/>
-      <c r="G79" s="61"/>
-      <c r="H79" s="61"/>
+      <c r="E79" s="61"/>
+      <c r="F79" s="66"/>
+      <c r="G79" s="67" t="s">
+        <v>103</v>
+      </c>
+      <c r="H79" s="39">
+        <v>225.07</v>
+      </c>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
@@ -3494,9 +3525,11 @@
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="1"/>
       <c r="B80" s="61"/>
-      <c r="C80" s="61"/>
+      <c r="C80" s="19" t="s">
+        <v>91</v>
+      </c>
       <c r="D80" s="61"/>
-      <c r="E80" s="61"/>
+      <c r="E80" s="60"/>
       <c r="F80" s="61"/>
       <c r="G80" s="61"/>
       <c r="H80" s="61"/>
@@ -3521,13 +3554,11 @@
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="1"/>
-      <c r="B81" s="62" t="s">
-        <v>101</v>
-      </c>
+      <c r="B81" s="61"/>
       <c r="C81" s="61"/>
       <c r="D81" s="61"/>
       <c r="E81" s="61"/>
-      <c r="F81" s="63"/>
+      <c r="F81" s="61"/>
       <c r="G81" s="61"/>
       <c r="H81" s="61"/>
       <c r="I81" s="1"/>
@@ -3551,18 +3582,15 @@
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="1"/>
-      <c r="C82" s="64" t="s">
-        <v>102</v>
+      <c r="B82" s="62" t="s">
+        <v>104</v>
       </c>
-      <c r="D82" s="65"/>
-      <c r="E82" s="65"/>
-      <c r="F82" s="66"/>
-      <c r="G82" s="67" t="s">
-        <v>103</v>
-      </c>
-      <c r="H82" s="39">
-        <v>197.99</v>
-      </c>
+      <c r="C82" s="61"/>
+      <c r="D82" s="61"/>
+      <c r="E82" s="61"/>
+      <c r="F82" s="63"/>
+      <c r="G82" s="61"/>
+      <c r="H82" s="61"/>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
@@ -3584,14 +3612,11 @@
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="1"/>
-      <c r="B83" s="19" t="s">
-        <v>104</v>
-      </c>
       <c r="C83" s="64" t="s">
         <v>105</v>
       </c>
-      <c r="D83" s="61"/>
-      <c r="E83" s="61"/>
+      <c r="D83" s="65"/>
+      <c r="E83" s="65"/>
       <c r="F83" s="66"/>
       <c r="G83" s="67" t="s">
         <v>106</v>
@@ -3620,17 +3645,21 @@
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="1"/>
-      <c r="B84" s="61"/>
-      <c r="C84" s="19" t="s">
-        <v>88</v>
+      <c r="B84" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C84" s="64" t="s">
+        <v>108</v>
       </c>
       <c r="D84" s="61"/>
-      <c r="E84" s="60">
+      <c r="E84" s="61"/>
+      <c r="F84" s="66"/>
+      <c r="G84" s="67" t="s">
+        <v>109</v>
+      </c>
+      <c r="H84" s="39">
         <v>197.99</v>
       </c>
-      <c r="F84" s="61"/>
-      <c r="G84" s="61"/>
-      <c r="H84" s="61"/>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
@@ -3653,9 +3682,13 @@
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="1"/>
       <c r="B85" s="61"/>
-      <c r="C85" s="61"/>
+      <c r="C85" s="19" t="s">
+        <v>91</v>
+      </c>
       <c r="D85" s="61"/>
-      <c r="E85" s="61"/>
+      <c r="E85" s="60">
+        <v>197.99</v>
+      </c>
       <c r="F85" s="61"/>
       <c r="G85" s="61"/>
       <c r="H85" s="61"/>
@@ -3680,13 +3713,13 @@
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="1"/>
-      <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
+      <c r="B86" s="61"/>
+      <c r="C86" s="61"/>
+      <c r="D86" s="61"/>
+      <c r="E86" s="61"/>
+      <c r="F86" s="61"/>
+      <c r="G86" s="61"/>
+      <c r="H86" s="61"/>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
       <c r="K86" s="1"/>
@@ -3708,15 +3741,13 @@
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="1"/>
-      <c r="B87" s="62" t="s">
-        <v>107</v>
-      </c>
-      <c r="C87" s="61"/>
-      <c r="D87" s="61"/>
-      <c r="E87" s="61"/>
-      <c r="F87" s="63"/>
-      <c r="G87" s="61"/>
-      <c r="H87" s="61"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
       <c r="K87" s="1"/>
@@ -3738,21 +3769,15 @@
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c r="A88" s="1"/>
-      <c r="B88" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="C88" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="D88" s="65"/>
-      <c r="E88" s="65"/>
-      <c r="F88" s="66"/>
-      <c r="G88" s="67" t="s">
+      <c r="B88" s="62" t="s">
         <v>110</v>
       </c>
-      <c r="H88" s="39">
-        <v>186.89</v>
-      </c>
+      <c r="C88" s="61"/>
+      <c r="D88" s="61"/>
+      <c r="E88" s="61"/>
+      <c r="F88" s="63"/>
+      <c r="G88" s="61"/>
+      <c r="H88" s="61"/>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
@@ -3780,14 +3805,14 @@
       <c r="C89" s="64" t="s">
         <v>112</v>
       </c>
-      <c r="D89" s="61"/>
-      <c r="E89" s="61"/>
+      <c r="D89" s="65"/>
+      <c r="E89" s="65"/>
       <c r="F89" s="66"/>
       <c r="G89" s="67" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="H89" s="39">
-        <v>92.31</v>
+        <v>186.89</v>
       </c>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
@@ -3810,17 +3835,21 @@
     </row>
     <row r="90" ht="14.25" customHeight="1">
       <c r="A90" s="1"/>
-      <c r="B90" s="61"/>
-      <c r="C90" s="19" t="s">
-        <v>88</v>
+      <c r="B90" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C90" s="64" t="s">
+        <v>115</v>
       </c>
       <c r="D90" s="61"/>
-      <c r="E90" s="60">
-        <v>186.89</v>
+      <c r="E90" s="61"/>
+      <c r="F90" s="66"/>
+      <c r="G90" s="67" t="s">
+        <v>16</v>
       </c>
-      <c r="F90" s="61"/>
-      <c r="G90" s="61"/>
-      <c r="H90" s="61"/>
+      <c r="H90" s="39">
+        <v>92.31</v>
+      </c>
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
       <c r="K90" s="1"/>
@@ -3843,9 +3872,13 @@
     <row r="91" ht="14.25" customHeight="1">
       <c r="A91" s="1"/>
       <c r="B91" s="61"/>
-      <c r="C91" s="61"/>
+      <c r="C91" s="19" t="s">
+        <v>91</v>
+      </c>
       <c r="D91" s="61"/>
-      <c r="E91" s="61"/>
+      <c r="E91" s="60">
+        <v>186.89</v>
+      </c>
       <c r="F91" s="61"/>
       <c r="G91" s="61"/>
       <c r="H91" s="61"/>
@@ -3870,13 +3903,11 @@
     </row>
     <row r="92" ht="14.25" customHeight="1">
       <c r="A92" s="1"/>
-      <c r="B92" s="50" t="s">
-        <v>113</v>
-      </c>
+      <c r="B92" s="61"/>
       <c r="C92" s="61"/>
       <c r="D92" s="61"/>
       <c r="E92" s="61"/>
-      <c r="F92" s="63"/>
+      <c r="F92" s="61"/>
       <c r="G92" s="61"/>
       <c r="H92" s="61"/>
       <c r="I92" s="1"/>
@@ -3900,19 +3931,15 @@
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c r="A93" s="1"/>
-      <c r="B93" s="1"/>
-      <c r="C93" s="64" t="s">
-        <v>114</v>
+      <c r="B93" s="50" t="s">
+        <v>116</v>
       </c>
-      <c r="D93" s="65"/>
-      <c r="E93" s="65"/>
-      <c r="F93" s="66"/>
-      <c r="G93" s="67" t="s">
-        <v>115</v>
-      </c>
-      <c r="H93" s="39">
-        <v>186.89</v>
-      </c>
+      <c r="C93" s="61"/>
+      <c r="D93" s="61"/>
+      <c r="E93" s="61"/>
+      <c r="F93" s="63"/>
+      <c r="G93" s="61"/>
+      <c r="H93" s="61"/>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
@@ -3934,20 +3961,18 @@
     </row>
     <row r="94" ht="14.25" customHeight="1">
       <c r="A94" s="1"/>
-      <c r="B94" s="19" t="s">
-        <v>116</v>
+      <c r="B94" s="1"/>
+      <c r="C94" s="64" t="s">
+        <v>117</v>
       </c>
-      <c r="C94" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="D94" s="61"/>
-      <c r="E94" s="61"/>
+      <c r="D94" s="65"/>
+      <c r="E94" s="65"/>
       <c r="F94" s="66"/>
       <c r="G94" s="67" t="s">
-        <v>53</v>
+        <v>118</v>
       </c>
       <c r="H94" s="39">
-        <v>92.31</v>
+        <v>186.89</v>
       </c>
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
@@ -3970,17 +3995,21 @@
     </row>
     <row r="95" ht="14.25" customHeight="1">
       <c r="A95" s="1"/>
-      <c r="B95" s="61"/>
-      <c r="C95" s="19" t="s">
-        <v>88</v>
+      <c r="B95" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C95" s="23" t="s">
+        <v>52</v>
       </c>
       <c r="D95" s="61"/>
-      <c r="E95" s="60">
-        <v>186.89</v>
+      <c r="E95" s="61"/>
+      <c r="F95" s="66"/>
+      <c r="G95" s="67" t="s">
+        <v>53</v>
       </c>
-      <c r="F95" s="61"/>
-      <c r="G95" s="61"/>
-      <c r="H95" s="61"/>
+      <c r="H95" s="39">
+        <v>92.31</v>
+      </c>
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
       <c r="K95" s="1"/>
@@ -4002,13 +4031,17 @@
     </row>
     <row r="96" ht="14.25" customHeight="1">
       <c r="A96" s="1"/>
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
+      <c r="B96" s="61"/>
+      <c r="C96" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D96" s="61"/>
+      <c r="E96" s="60">
+        <v>186.89</v>
+      </c>
+      <c r="F96" s="61"/>
+      <c r="G96" s="61"/>
+      <c r="H96" s="61"/>
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
@@ -4058,13 +4091,15 @@
     </row>
     <row r="98" ht="14.25" customHeight="1">
       <c r="A98" s="1"/>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
+      <c r="B98" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="C98" s="61"/>
+      <c r="D98" s="61"/>
+      <c r="E98" s="61"/>
+      <c r="F98" s="63"/>
+      <c r="G98" s="61"/>
+      <c r="H98" s="61"/>
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>
@@ -4086,13 +4121,19 @@
     </row>
     <row r="99" ht="14.25" customHeight="1">
       <c r="A99" s="1"/>
-      <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="2"/>
+      <c r="B99" s="1"/>
+      <c r="C99" s="64" t="s">
+        <v>121</v>
+      </c>
+      <c r="D99" s="65"/>
+      <c r="E99" s="65"/>
+      <c r="F99" s="66"/>
+      <c r="G99" s="67" t="s">
+        <v>122</v>
+      </c>
+      <c r="H99" s="39">
+        <v>186.89</v>
+      </c>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
@@ -4114,13 +4155,21 @@
     </row>
     <row r="100" ht="14.25" customHeight="1">
       <c r="A100" s="1"/>
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-      <c r="H100" s="2"/>
+      <c r="B100" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C100" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="D100" s="61"/>
+      <c r="E100" s="61"/>
+      <c r="F100" s="66"/>
+      <c r="G100" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="H100" s="39">
+        <v>92.31</v>
+      </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
       <c r="K100" s="1"/>
@@ -4142,13 +4191,17 @@
     </row>
     <row r="101" ht="14.25" customHeight="1">
       <c r="A101" s="1"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="2"/>
+      <c r="B101" s="61"/>
+      <c r="C101" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D101" s="61"/>
+      <c r="E101" s="60">
+        <v>186.89</v>
+      </c>
+      <c r="F101" s="61"/>
+      <c r="G101" s="61"/>
+      <c r="H101" s="61"/>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
@@ -26794,6 +26847,12 @@
     </row>
     <row r="910" ht="14.25" customHeight="1">
       <c r="A910" s="1"/>
+      <c r="B910" s="2"/>
+      <c r="C910" s="2"/>
+      <c r="D910" s="2"/>
+      <c r="E910" s="2"/>
+      <c r="F910" s="2"/>
+      <c r="G910" s="2"/>
       <c r="H910" s="2"/>
       <c r="I910" s="1"/>
       <c r="J910" s="1"/>
@@ -26816,6 +26875,8 @@
     </row>
     <row r="911" ht="14.25" customHeight="1">
       <c r="A911" s="1"/>
+      <c r="H911" s="2"/>
+      <c r="I911" s="1"/>
       <c r="J911" s="1"/>
       <c r="K911" s="1"/>
       <c r="L911" s="1"/>
@@ -26834,6 +26895,26 @@
       <c r="Y911" s="1"/>
       <c r="Z911" s="1"/>
     </row>
+    <row r="912" ht="14.25" customHeight="1">
+      <c r="A912" s="1"/>
+      <c r="J912" s="1"/>
+      <c r="K912" s="1"/>
+      <c r="L912" s="1"/>
+      <c r="M912" s="1"/>
+      <c r="N912" s="1"/>
+      <c r="O912" s="1"/>
+      <c r="P912" s="1"/>
+      <c r="Q912" s="1"/>
+      <c r="R912" s="1"/>
+      <c r="S912" s="1"/>
+      <c r="T912" s="1"/>
+      <c r="U912" s="1"/>
+      <c r="V912" s="1"/>
+      <c r="W912" s="1"/>
+      <c r="X912" s="1"/>
+      <c r="Y912" s="1"/>
+      <c r="Z912" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="C2:H2"/>

--- a/base_backoffice.xlsx
+++ b/base_backoffice.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Znk0HmE6canBtG9VRSo5I523/d94sfmHi8N3K6YxTPg="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="QlR5TpxCWX0ilEjbHSV+CtHjtUETXozvNHtFdX6Jhyw="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="129">
   <si>
     <t>RELATÓRIO BACKOFFICE</t>
   </si>
@@ -62,6 +62,15 @@
   </si>
   <si>
     <t>Thauane</t>
+  </si>
+  <si>
+    <t>Recebe a partir de 01/06/2026</t>
+  </si>
+  <si>
+    <t>Glaucia Abreu (217313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glaucia </t>
   </si>
   <si>
     <t>Jessica Santana (211901)</t>
@@ -1389,21 +1398,19 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="23" t="s">
+      <c r="B13" s="26" t="s">
         <v>15</v>
       </c>
+      <c r="C13" s="23" t="s">
+        <v>16</v>
+      </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="27">
-        <v>595.18</v>
-      </c>
+      <c r="E13" s="27"/>
       <c r="F13" s="1"/>
       <c r="G13" s="24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
-      <c r="H13" s="18">
-        <v>595.18</v>
-      </c>
+      <c r="H13" s="18"/>
       <c r="J13" s="1"/>
       <c r="K13" s="25"/>
       <c r="L13" s="1"/>
@@ -1424,12 +1431,21 @@
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="2"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="27">
+        <v>595.18</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="18">
+        <v>595.18</v>
+      </c>
       <c r="J14" s="1"/>
       <c r="K14" s="25"/>
       <c r="L14" s="1"/>
@@ -1450,18 +1466,14 @@
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="11" t="s">
-        <v>17</v>
-      </c>
+      <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
+      <c r="D15" s="12"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="1"/>
+      <c r="F15" s="28"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="1"/>
       <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
+      <c r="K15" s="25"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -1480,21 +1492,17 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="13" t="s">
-        <v>18</v>
+      <c r="B16" s="11" t="s">
+        <v>20</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" s="32">
-        <v>866.09</v>
-      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="28"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="33"/>
+      <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -1516,13 +1524,13 @@
       <c r="A17" s="1"/>
       <c r="B17" s="2"/>
       <c r="C17" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="12"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="29"/>
       <c r="F17" s="30"/>
-      <c r="G17" s="24" t="s">
-        <v>21</v>
+      <c r="G17" s="31" t="s">
+        <v>22</v>
       </c>
       <c r="H17" s="32">
         <v>866.09</v>
@@ -1548,13 +1556,12 @@
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="23" t="s">
+      <c r="B18" s="2"/>
+      <c r="C18" s="13" t="s">
         <v>23</v>
       </c>
       <c r="D18" s="2"/>
+      <c r="E18" s="12"/>
       <c r="F18" s="30"/>
       <c r="G18" s="24" t="s">
         <v>24</v>
@@ -1563,7 +1570,7 @@
         <v>866.09</v>
       </c>
       <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
+      <c r="J18" s="33"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -1583,15 +1590,20 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="19" t="s">
+      <c r="B19" s="19" t="s">
         <v>25</v>
       </c>
+      <c r="C19" s="23" t="s">
+        <v>26</v>
+      </c>
       <c r="D19" s="2"/>
-      <c r="E19" s="34">
+      <c r="F19" s="30"/>
+      <c r="G19" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="32">
         <v>866.09</v>
       </c>
-      <c r="F19" s="2"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -1613,12 +1625,15 @@
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="C20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="19" t="s">
+        <v>28</v>
+      </c>
       <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="1"/>
+      <c r="E20" s="34">
+        <v>866.09</v>
+      </c>
+      <c r="F20" s="2"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -1640,15 +1655,12 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="11" t="s">
-        <v>26</v>
-      </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="1"/>
       <c r="G21" s="2"/>
-      <c r="H21" s="28"/>
+      <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -1670,21 +1682,17 @@
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="37"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="38" t="s">
+      <c r="B22" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H22" s="39"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="28"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="2"/>
+      <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -1704,21 +1712,21 @@
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="36" t="s">
+      <c r="B23" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="40" t="s">
+      <c r="C23" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="H23" s="39">
-        <v>956.23</v>
+      <c r="D23" s="37"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="38" t="s">
+        <v>32</v>
       </c>
+      <c r="H23" s="39"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="41"/>
+      <c r="J23" s="2"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -1738,20 +1746,18 @@
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="42" t="s">
+      <c r="B24" s="2"/>
+      <c r="C24" s="36" t="s">
         <v>33</v>
       </c>
       <c r="D24" s="2"/>
-      <c r="E24" s="12"/>
+      <c r="E24" s="2"/>
       <c r="F24" s="30"/>
-      <c r="G24" s="24" t="s">
+      <c r="G24" s="40" t="s">
         <v>34</v>
       </c>
       <c r="H24" s="39">
-        <v>950.35</v>
+        <v>956.23</v>
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="41"/>
@@ -1774,18 +1780,20 @@
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="12"/>
+      <c r="B25" s="35" t="s">
+        <v>35</v>
+      </c>
       <c r="C25" s="42" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="12"/>
       <c r="F25" s="30"/>
       <c r="G25" s="24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H25" s="39">
-        <v>956.23</v>
+        <v>950.35</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="41"/>
@@ -1808,16 +1816,22 @@
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="19" t="s">
-        <v>37</v>
+      <c r="B26" s="12"/>
+      <c r="C26" s="42" t="s">
+        <v>38</v>
       </c>
       <c r="D26" s="2"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="H26" s="39">
+        <v>956.23</v>
+      </c>
       <c r="I26" s="1"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="25"/>
+      <c r="J26" s="41"/>
+      <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
@@ -1837,15 +1851,15 @@
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
+      <c r="C27" s="19" t="s">
+        <v>40</v>
+      </c>
       <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="12"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="25"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
@@ -1862,17 +1876,15 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" ht="13.5" customHeight="1">
+    <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="11" t="s">
-        <v>38</v>
-      </c>
+      <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
-      <c r="F28" s="1"/>
+      <c r="F28" s="2"/>
       <c r="G28" s="2"/>
-      <c r="H28" s="30"/>
+      <c r="H28" s="2"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -1892,21 +1904,17 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" ht="14.25" customHeight="1">
+    <row r="29" ht="13.5" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="23" t="s">
-        <v>39</v>
+      <c r="B29" s="11" t="s">
+        <v>41</v>
       </c>
-      <c r="D29" s="43"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="45" t="s">
-        <v>40</v>
-      </c>
-      <c r="H29" s="46">
-        <v>306.21</v>
-      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="30"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
@@ -1930,13 +1938,13 @@
       <c r="A30" s="1"/>
       <c r="B30" s="12"/>
       <c r="C30" s="23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
-      <c r="D30" s="2"/>
-      <c r="E30" s="47"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="44"/>
       <c r="F30" s="30"/>
-      <c r="G30" s="24" t="s">
-        <v>42</v>
+      <c r="G30" s="45" t="s">
+        <v>43</v>
       </c>
       <c r="H30" s="46">
         <v>306.21</v>
@@ -1962,19 +1970,19 @@
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="48" t="s">
-        <v>43</v>
-      </c>
+      <c r="B31" s="12"/>
       <c r="C31" s="23" t="s">
         <v>44</v>
       </c>
       <c r="D31" s="2"/>
-      <c r="E31" s="34">
+      <c r="E31" s="47"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="H31" s="46">
         <v>306.21</v>
       </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="12"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -1996,14 +2004,19 @@
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="19" t="s">
-        <v>45</v>
+      <c r="B32" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>47</v>
       </c>
       <c r="D32" s="2"/>
-      <c r="E32" s="49"/>
+      <c r="E32" s="34">
+        <v>306.21</v>
+      </c>
       <c r="F32" s="2"/>
-      <c r="H32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="12"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -2026,11 +2039,12 @@
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
+      <c r="C33" s="19" t="s">
+        <v>48</v>
+      </c>
       <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
+      <c r="E33" s="49"/>
       <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
@@ -2053,15 +2067,13 @@
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="50" t="s">
-        <v>46</v>
-      </c>
+      <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="1"/>
+      <c r="F34" s="2"/>
       <c r="G34" s="2"/>
-      <c r="H34" s="12"/>
+      <c r="H34" s="2"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -2083,19 +2095,15 @@
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="23" t="s">
-        <v>44</v>
+      <c r="B35" s="50" t="s">
+        <v>49</v>
       </c>
-      <c r="D35" s="23"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="H35" s="52">
-        <v>395.56</v>
-      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="12"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -2117,16 +2125,14 @@
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="19" t="s">
-        <v>48</v>
+      <c r="B36" s="12"/>
+      <c r="C36" s="23" t="s">
+        <v>47</v>
       </c>
-      <c r="C36" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="D36" s="2"/>
-      <c r="E36" s="47"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="51"/>
       <c r="F36" s="30"/>
-      <c r="G36" s="24" t="s">
+      <c r="G36" s="31" t="s">
         <v>50</v>
       </c>
       <c r="H36" s="52">
@@ -2160,13 +2166,13 @@
         <v>52</v>
       </c>
       <c r="D37" s="2"/>
-      <c r="E37" s="12"/>
+      <c r="E37" s="47"/>
       <c r="F37" s="30"/>
       <c r="G37" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H37" s="53">
-        <v>2.9</v>
+      <c r="H37" s="52">
+        <v>395.56</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -2189,15 +2195,21 @@
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="19" t="s">
-        <v>25</v>
+      <c r="B38" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>55</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="12"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="H38" s="53">
+        <v>2.9</v>
+      </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -2220,11 +2232,11 @@
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
+      <c r="C39" s="19" t="s">
+        <v>28</v>
+      </c>
       <c r="D39" s="2"/>
-      <c r="E39" s="27">
-        <v>395.56</v>
-      </c>
+      <c r="E39" s="12"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
@@ -2252,7 +2264,9 @@
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
+      <c r="E40" s="27">
+        <v>395.56</v>
+      </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
@@ -2277,14 +2291,13 @@
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="50" t="s">
-        <v>54</v>
-      </c>
+      <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
-      <c r="F41" s="1"/>
+      <c r="F41" s="2"/>
       <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -2306,19 +2319,14 @@
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="1"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="23" t="s">
-        <v>55</v>
+      <c r="B42" s="50" t="s">
+        <v>57</v>
       </c>
-      <c r="D42" s="23"/>
-      <c r="E42" s="51"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="H42" s="32">
-        <v>407.03</v>
-      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="2"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -2342,13 +2350,13 @@
       <c r="A43" s="1"/>
       <c r="B43" s="12"/>
       <c r="C43" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
-      <c r="D43" s="2"/>
-      <c r="E43" s="47"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="51"/>
       <c r="F43" s="30"/>
-      <c r="G43" s="24" t="s">
-        <v>58</v>
+      <c r="G43" s="31" t="s">
+        <v>59</v>
       </c>
       <c r="H43" s="32">
         <v>407.03</v>
@@ -2374,20 +2382,18 @@
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="1"/>
-      <c r="B44" s="19" t="s">
-        <v>59</v>
-      </c>
+      <c r="B44" s="12"/>
       <c r="C44" s="23" t="s">
         <v>60</v>
       </c>
       <c r="D44" s="2"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="2"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="30"/>
       <c r="G44" s="24" t="s">
         <v>61</v>
       </c>
       <c r="H44" s="32">
-        <v>160.34</v>
+        <v>407.03</v>
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
@@ -2410,15 +2416,21 @@
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="1"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="19" t="s">
-        <v>25</v>
+      <c r="B45" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" s="23" t="s">
+        <v>63</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="12"/>
       <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
+      <c r="G45" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="H45" s="32">
+        <v>160.34</v>
+      </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
@@ -2441,11 +2453,11 @@
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="1"/>
       <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
+      <c r="C46" s="19" t="s">
+        <v>28</v>
+      </c>
       <c r="D46" s="2"/>
-      <c r="E46" s="34">
-        <v>407.03</v>
-      </c>
+      <c r="E46" s="12"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -2473,7 +2485,9 @@
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
+      <c r="E47" s="34">
+        <v>407.03</v>
+      </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -2498,14 +2512,13 @@
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="1"/>
-      <c r="B48" s="50" t="s">
-        <v>62</v>
-      </c>
+      <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
-      <c r="F48" s="1"/>
+      <c r="F48" s="2"/>
       <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -2527,19 +2540,14 @@
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="C49" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="D49" s="23"/>
-      <c r="E49" s="51"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="31" t="s">
+      <c r="B49" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="H49" s="54"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="2"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -2561,21 +2569,19 @@
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="1"/>
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="19" t="s">
         <v>66</v>
       </c>
       <c r="C50" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="D50" s="2"/>
-      <c r="E50" s="55"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="51"/>
       <c r="F50" s="30"/>
-      <c r="G50" s="45" t="s">
+      <c r="G50" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="H50" s="18">
-        <v>390.96</v>
-      </c>
+      <c r="H50" s="54"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -2597,15 +2603,17 @@
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="1"/>
-      <c r="B51" s="12"/>
+      <c r="B51" s="12" t="s">
+        <v>69</v>
+      </c>
       <c r="C51" s="23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="55"/>
       <c r="F51" s="30"/>
-      <c r="G51" s="24" t="s">
-        <v>11</v>
+      <c r="G51" s="45" t="s">
+        <v>71</v>
       </c>
       <c r="H51" s="18">
         <v>390.96</v>
@@ -2631,15 +2639,19 @@
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="1"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="19" t="s">
-        <v>25</v>
+      <c r="B52" s="12"/>
+      <c r="C52" s="23" t="s">
+        <v>72</v>
       </c>
       <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
+      <c r="E52" s="55"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H52" s="18">
+        <v>390.96</v>
+      </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -2662,11 +2674,11 @@
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="1"/>
       <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
+      <c r="C53" s="19" t="s">
+        <v>28</v>
+      </c>
       <c r="D53" s="2"/>
-      <c r="E53" s="27">
-        <v>390.96</v>
-      </c>
+      <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
@@ -2691,14 +2703,15 @@
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="1"/>
-      <c r="B54" s="50" t="s">
-        <v>70</v>
-      </c>
+      <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="1"/>
+      <c r="E54" s="27">
+        <v>390.96</v>
+      </c>
+      <c r="F54" s="2"/>
       <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
@@ -2720,19 +2733,14 @@
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="1"/>
-      <c r="B55" s="12"/>
-      <c r="C55" s="23" t="s">
-        <v>71</v>
+      <c r="B55" s="50" t="s">
+        <v>73</v>
       </c>
-      <c r="D55" s="23"/>
-      <c r="E55" s="51"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="H55" s="56">
-        <v>984.22</v>
-      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="2"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
@@ -2756,13 +2764,13 @@
       <c r="A56" s="1"/>
       <c r="B56" s="12"/>
       <c r="C56" s="23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
-      <c r="D56" s="2"/>
-      <c r="E56" s="47"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="51"/>
       <c r="F56" s="30"/>
-      <c r="G56" s="24" t="s">
-        <v>24</v>
+      <c r="G56" s="31" t="s">
+        <v>75</v>
       </c>
       <c r="H56" s="56">
         <v>984.22</v>
@@ -2790,13 +2798,13 @@
       <c r="A57" s="1"/>
       <c r="B57" s="12"/>
       <c r="C57" s="23" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="47"/>
       <c r="F57" s="30"/>
       <c r="G57" s="24" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="H57" s="56">
         <v>984.22</v>
@@ -2822,17 +2830,19 @@
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="1"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="19" t="s">
-        <v>25</v>
+      <c r="B58" s="12"/>
+      <c r="C58" s="23" t="s">
+        <v>77</v>
       </c>
       <c r="D58" s="2"/>
-      <c r="E58" s="27">
+      <c r="E58" s="47"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="H58" s="56">
         <v>984.22</v>
       </c>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="12"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
@@ -2855,12 +2865,16 @@
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="1"/>
       <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
+      <c r="C59" s="19" t="s">
+        <v>28</v>
+      </c>
       <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
+      <c r="E59" s="27">
+        <v>984.22</v>
+      </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
+      <c r="H59" s="12"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
@@ -2882,14 +2896,13 @@
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="1"/>
-      <c r="B60" s="50" t="s">
-        <v>76</v>
-      </c>
+      <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
-      <c r="F60" s="1"/>
+      <c r="F60" s="2"/>
       <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
@@ -2911,19 +2924,14 @@
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="1"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="23" t="s">
-        <v>77</v>
+      <c r="B61" s="50" t="s">
+        <v>79</v>
       </c>
-      <c r="D61" s="23"/>
-      <c r="E61" s="51"/>
-      <c r="F61" s="30"/>
-      <c r="G61" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="H61" s="32">
-        <v>579.37</v>
-      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="2"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
@@ -2947,13 +2955,13 @@
       <c r="A62" s="1"/>
       <c r="B62" s="12"/>
       <c r="C62" s="23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
-      <c r="D62" s="2"/>
-      <c r="E62" s="47"/>
+      <c r="D62" s="23"/>
+      <c r="E62" s="51"/>
       <c r="F62" s="30"/>
-      <c r="G62" s="24" t="s">
-        <v>80</v>
+      <c r="G62" s="31" t="s">
+        <v>81</v>
       </c>
       <c r="H62" s="32">
         <v>579.37</v>
@@ -2979,20 +2987,18 @@
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="1"/>
-      <c r="B63" s="19" t="s">
-        <v>51</v>
-      </c>
+      <c r="B63" s="12"/>
       <c r="C63" s="23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D63" s="2"/>
-      <c r="E63" s="12"/>
-      <c r="F63" s="2"/>
+      <c r="E63" s="47"/>
+      <c r="F63" s="30"/>
       <c r="G63" s="24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H63" s="32">
-        <v>216.22</v>
+        <v>579.37</v>
       </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
@@ -3015,15 +3021,21 @@
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="1"/>
-      <c r="B64" s="12"/>
-      <c r="C64" s="19" t="s">
-        <v>25</v>
+      <c r="B64" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C64" s="23" t="s">
+        <v>84</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="12"/>
       <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="12"/>
+      <c r="G64" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="H64" s="32">
+        <v>216.22</v>
+      </c>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
@@ -3045,15 +3057,15 @@
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="1"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
+      <c r="B65" s="12"/>
+      <c r="C65" s="19" t="s">
+        <v>28</v>
+      </c>
       <c r="D65" s="2"/>
-      <c r="E65" s="34">
-        <v>579.37</v>
-      </c>
+      <c r="E65" s="12"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
+      <c r="H65" s="12"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
@@ -3075,15 +3087,15 @@
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="1"/>
-      <c r="B66" s="50" t="s">
-        <v>83</v>
-      </c>
+      <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="6"/>
+      <c r="E66" s="34">
+        <v>579.37</v>
+      </c>
+      <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-      <c r="H66" s="12"/>
+      <c r="H66" s="2"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
@@ -3105,19 +3117,15 @@
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="1"/>
-      <c r="B67" s="26"/>
-      <c r="C67" s="23" t="s">
-        <v>84</v>
+      <c r="B67" s="50" t="s">
+        <v>86</v>
       </c>
-      <c r="D67" s="13"/>
-      <c r="E67" s="57"/>
-      <c r="F67" s="30"/>
-      <c r="G67" s="58" t="s">
-        <v>85</v>
-      </c>
-      <c r="H67" s="39">
-        <v>937.68</v>
-      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="12"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
@@ -3139,15 +3147,15 @@
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="1"/>
-      <c r="B68" s="12"/>
-      <c r="C68" s="13" t="s">
-        <v>86</v>
+      <c r="B68" s="26"/>
+      <c r="C68" s="23" t="s">
+        <v>87</v>
       </c>
-      <c r="D68" s="59"/>
-      <c r="E68" s="2"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="57"/>
       <c r="F68" s="30"/>
       <c r="G68" s="58" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H68" s="39">
         <v>937.68</v>
@@ -3173,10 +3181,8 @@
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="1"/>
-      <c r="B69" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="C69" s="23" t="s">
+      <c r="B69" s="12"/>
+      <c r="C69" s="13" t="s">
         <v>89</v>
       </c>
       <c r="D69" s="59"/>
@@ -3185,7 +3191,9 @@
       <c r="G69" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="H69" s="39"/>
+      <c r="H69" s="39">
+        <v>937.68</v>
+      </c>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
@@ -3207,16 +3215,19 @@
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="1"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="19" t="s">
+      <c r="B70" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="D70" s="2"/>
-      <c r="E70" s="34">
-        <v>937.68</v>
+      <c r="C70" s="23" t="s">
+        <v>92</v>
       </c>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
+      <c r="D70" s="59"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="58" t="s">
+        <v>93</v>
+      </c>
+      <c r="H70" s="39"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
@@ -3239,12 +3250,15 @@
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="1"/>
       <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
+      <c r="C71" s="19" t="s">
+        <v>94</v>
+      </c>
       <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
+      <c r="E71" s="34">
+        <v>937.68</v>
+      </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
@@ -3266,15 +3280,13 @@
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="1"/>
-      <c r="B72" s="50" t="s">
-        <v>92</v>
-      </c>
+      <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
-      <c r="F72" s="6"/>
+      <c r="F72" s="2"/>
       <c r="G72" s="2"/>
-      <c r="H72" s="12"/>
+      <c r="H72" s="2"/>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
@@ -3296,19 +3308,15 @@
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="1"/>
-      <c r="B73" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="C73" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="D73" s="43"/>
-      <c r="E73" s="57"/>
-      <c r="F73" s="30"/>
-      <c r="G73" s="58" t="s">
+      <c r="B73" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="H73" s="39"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="12"/>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
@@ -3330,19 +3338,19 @@
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="1"/>
-      <c r="B74" s="12"/>
-      <c r="C74" s="23" t="s">
+      <c r="B74" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="D74" s="2"/>
-      <c r="E74" s="12"/>
+      <c r="C74" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="D74" s="43"/>
+      <c r="E74" s="57"/>
       <c r="F74" s="30"/>
       <c r="G74" s="58" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
-      <c r="H74" s="39">
-        <v>27.64</v>
-      </c>
+      <c r="H74" s="39"/>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
@@ -3362,19 +3370,21 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
     </row>
-    <row r="75" ht="17.25" customHeight="1">
+    <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="1"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="19" t="s">
-        <v>91</v>
+      <c r="B75" s="12"/>
+      <c r="C75" s="23" t="s">
+        <v>99</v>
       </c>
       <c r="D75" s="2"/>
-      <c r="E75" s="60">
+      <c r="E75" s="12"/>
+      <c r="F75" s="30"/>
+      <c r="G75" s="58" t="s">
+        <v>100</v>
+      </c>
+      <c r="H75" s="39">
         <v>27.64</v>
       </c>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
@@ -3394,81 +3404,77 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row r="76" ht="14.25" customHeight="1">
-      <c r="A76" s="61"/>
-      <c r="B76" s="61"/>
-      <c r="C76" s="61"/>
-      <c r="D76" s="61"/>
-      <c r="E76" s="61"/>
-      <c r="F76" s="61"/>
-      <c r="G76" s="61"/>
-      <c r="H76" s="61"/>
-      <c r="I76" s="61"/>
-      <c r="J76" s="61"/>
-      <c r="K76" s="61"/>
-      <c r="L76" s="61"/>
-      <c r="M76" s="61"/>
-      <c r="N76" s="61"/>
-      <c r="O76" s="61"/>
-      <c r="P76" s="61"/>
-      <c r="Q76" s="61"/>
-      <c r="R76" s="61"/>
-      <c r="S76" s="61"/>
-      <c r="T76" s="61"/>
-      <c r="U76" s="61"/>
-      <c r="V76" s="61"/>
-      <c r="W76" s="61"/>
-      <c r="X76" s="61"/>
-      <c r="Y76" s="61"/>
-      <c r="Z76" s="61"/>
+    <row r="76" ht="17.25" customHeight="1">
+      <c r="A76" s="1"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D76" s="2"/>
+      <c r="E76" s="60">
+        <v>27.64</v>
+      </c>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+      <c r="K76" s="1"/>
+      <c r="L76" s="1"/>
+      <c r="M76" s="1"/>
+      <c r="N76" s="1"/>
+      <c r="O76" s="1"/>
+      <c r="P76" s="1"/>
+      <c r="Q76" s="1"/>
+      <c r="R76" s="1"/>
+      <c r="S76" s="1"/>
+      <c r="T76" s="1"/>
+      <c r="U76" s="1"/>
+      <c r="V76" s="1"/>
+      <c r="W76" s="1"/>
+      <c r="X76" s="1"/>
+      <c r="Y76" s="1"/>
+      <c r="Z76" s="1"/>
     </row>
     <row r="77" ht="14.25" customHeight="1">
-      <c r="A77" s="1"/>
-      <c r="B77" s="62" t="s">
-        <v>98</v>
-      </c>
+      <c r="A77" s="61"/>
+      <c r="B77" s="61"/>
       <c r="C77" s="61"/>
       <c r="D77" s="61"/>
       <c r="E77" s="61"/>
-      <c r="F77" s="63"/>
+      <c r="F77" s="61"/>
       <c r="G77" s="61"/>
       <c r="H77" s="61"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
-      <c r="K77" s="1"/>
-      <c r="L77" s="1"/>
-      <c r="M77" s="1"/>
-      <c r="N77" s="1"/>
-      <c r="O77" s="1"/>
-      <c r="P77" s="1"/>
-      <c r="Q77" s="1"/>
-      <c r="R77" s="1"/>
-      <c r="S77" s="1"/>
-      <c r="T77" s="1"/>
-      <c r="U77" s="1"/>
-      <c r="V77" s="1"/>
-      <c r="W77" s="1"/>
-      <c r="X77" s="1"/>
-      <c r="Y77" s="1"/>
-      <c r="Z77" s="1"/>
+      <c r="I77" s="61"/>
+      <c r="J77" s="61"/>
+      <c r="K77" s="61"/>
+      <c r="L77" s="61"/>
+      <c r="M77" s="61"/>
+      <c r="N77" s="61"/>
+      <c r="O77" s="61"/>
+      <c r="P77" s="61"/>
+      <c r="Q77" s="61"/>
+      <c r="R77" s="61"/>
+      <c r="S77" s="61"/>
+      <c r="T77" s="61"/>
+      <c r="U77" s="61"/>
+      <c r="V77" s="61"/>
+      <c r="W77" s="61"/>
+      <c r="X77" s="61"/>
+      <c r="Y77" s="61"/>
+      <c r="Z77" s="61"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="1"/>
-      <c r="B78" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C78" s="64" t="s">
-        <v>100</v>
-      </c>
-      <c r="D78" s="65"/>
-      <c r="E78" s="65"/>
-      <c r="F78" s="66"/>
-      <c r="G78" s="67" t="s">
+      <c r="B78" s="62" t="s">
         <v>101</v>
       </c>
-      <c r="H78" s="39">
-        <v>225.07</v>
-      </c>
+      <c r="C78" s="61"/>
+      <c r="D78" s="61"/>
+      <c r="E78" s="61"/>
+      <c r="F78" s="63"/>
+      <c r="G78" s="61"/>
+      <c r="H78" s="61"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
@@ -3490,15 +3496,17 @@
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="1"/>
-      <c r="B79" s="61"/>
-      <c r="C79" s="64" t="s">
+      <c r="B79" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D79" s="61"/>
-      <c r="E79" s="61"/>
+      <c r="C79" s="64" t="s">
+        <v>103</v>
+      </c>
+      <c r="D79" s="65"/>
+      <c r="E79" s="65"/>
       <c r="F79" s="66"/>
       <c r="G79" s="67" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H79" s="39">
         <v>225.07</v>
@@ -3525,14 +3533,18 @@
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="1"/>
       <c r="B80" s="61"/>
-      <c r="C80" s="19" t="s">
-        <v>91</v>
+      <c r="C80" s="64" t="s">
+        <v>105</v>
       </c>
       <c r="D80" s="61"/>
-      <c r="E80" s="60"/>
-      <c r="F80" s="61"/>
-      <c r="G80" s="61"/>
-      <c r="H80" s="61"/>
+      <c r="E80" s="61"/>
+      <c r="F80" s="66"/>
+      <c r="G80" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="H80" s="39">
+        <v>225.07</v>
+      </c>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
@@ -3555,9 +3567,11 @@
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="1"/>
       <c r="B81" s="61"/>
-      <c r="C81" s="61"/>
+      <c r="C81" s="19" t="s">
+        <v>94</v>
+      </c>
       <c r="D81" s="61"/>
-      <c r="E81" s="61"/>
+      <c r="E81" s="60"/>
       <c r="F81" s="61"/>
       <c r="G81" s="61"/>
       <c r="H81" s="61"/>
@@ -3582,13 +3596,11 @@
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="1"/>
-      <c r="B82" s="62" t="s">
-        <v>104</v>
-      </c>
+      <c r="B82" s="61"/>
       <c r="C82" s="61"/>
       <c r="D82" s="61"/>
       <c r="E82" s="61"/>
-      <c r="F82" s="63"/>
+      <c r="F82" s="61"/>
       <c r="G82" s="61"/>
       <c r="H82" s="61"/>
       <c r="I82" s="1"/>
@@ -3612,18 +3624,15 @@
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="1"/>
-      <c r="C83" s="64" t="s">
-        <v>105</v>
+      <c r="B83" s="62" t="s">
+        <v>107</v>
       </c>
-      <c r="D83" s="65"/>
-      <c r="E83" s="65"/>
-      <c r="F83" s="66"/>
-      <c r="G83" s="67" t="s">
-        <v>106</v>
-      </c>
-      <c r="H83" s="39">
-        <v>197.99</v>
-      </c>
+      <c r="C83" s="61"/>
+      <c r="D83" s="61"/>
+      <c r="E83" s="61"/>
+      <c r="F83" s="63"/>
+      <c r="G83" s="61"/>
+      <c r="H83" s="61"/>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
@@ -3645,14 +3654,11 @@
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="1"/>
-      <c r="B84" s="19" t="s">
-        <v>107</v>
-      </c>
       <c r="C84" s="64" t="s">
         <v>108</v>
       </c>
-      <c r="D84" s="61"/>
-      <c r="E84" s="61"/>
+      <c r="D84" s="65"/>
+      <c r="E84" s="65"/>
       <c r="F84" s="66"/>
       <c r="G84" s="67" t="s">
         <v>109</v>
@@ -3681,17 +3687,21 @@
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="1"/>
-      <c r="B85" s="61"/>
-      <c r="C85" s="19" t="s">
-        <v>91</v>
+      <c r="B85" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="C85" s="64" t="s">
+        <v>111</v>
       </c>
       <c r="D85" s="61"/>
-      <c r="E85" s="60">
+      <c r="E85" s="61"/>
+      <c r="F85" s="66"/>
+      <c r="G85" s="67" t="s">
+        <v>112</v>
+      </c>
+      <c r="H85" s="39">
         <v>197.99</v>
       </c>
-      <c r="F85" s="61"/>
-      <c r="G85" s="61"/>
-      <c r="H85" s="61"/>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
@@ -3714,9 +3724,13 @@
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="1"/>
       <c r="B86" s="61"/>
-      <c r="C86" s="61"/>
+      <c r="C86" s="19" t="s">
+        <v>94</v>
+      </c>
       <c r="D86" s="61"/>
-      <c r="E86" s="61"/>
+      <c r="E86" s="60">
+        <v>197.99</v>
+      </c>
       <c r="F86" s="61"/>
       <c r="G86" s="61"/>
       <c r="H86" s="61"/>
@@ -3741,13 +3755,13 @@
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="1"/>
-      <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
+      <c r="B87" s="61"/>
+      <c r="C87" s="61"/>
+      <c r="D87" s="61"/>
+      <c r="E87" s="61"/>
+      <c r="F87" s="61"/>
+      <c r="G87" s="61"/>
+      <c r="H87" s="61"/>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
       <c r="K87" s="1"/>
@@ -3769,15 +3783,13 @@
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c r="A88" s="1"/>
-      <c r="B88" s="62" t="s">
-        <v>110</v>
-      </c>
-      <c r="C88" s="61"/>
-      <c r="D88" s="61"/>
-      <c r="E88" s="61"/>
-      <c r="F88" s="63"/>
-      <c r="G88" s="61"/>
-      <c r="H88" s="61"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
@@ -3799,21 +3811,15 @@
     </row>
     <row r="89" ht="14.25" customHeight="1">
       <c r="A89" s="1"/>
-      <c r="B89" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="C89" s="64" t="s">
-        <v>112</v>
-      </c>
-      <c r="D89" s="65"/>
-      <c r="E89" s="65"/>
-      <c r="F89" s="66"/>
-      <c r="G89" s="67" t="s">
+      <c r="B89" s="62" t="s">
         <v>113</v>
       </c>
-      <c r="H89" s="39">
-        <v>186.89</v>
-      </c>
+      <c r="C89" s="61"/>
+      <c r="D89" s="61"/>
+      <c r="E89" s="61"/>
+      <c r="F89" s="63"/>
+      <c r="G89" s="61"/>
+      <c r="H89" s="61"/>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
       <c r="K89" s="1"/>
@@ -3841,14 +3847,14 @@
       <c r="C90" s="64" t="s">
         <v>115</v>
       </c>
-      <c r="D90" s="61"/>
-      <c r="E90" s="61"/>
+      <c r="D90" s="65"/>
+      <c r="E90" s="65"/>
       <c r="F90" s="66"/>
       <c r="G90" s="67" t="s">
-        <v>16</v>
+        <v>116</v>
       </c>
       <c r="H90" s="39">
-        <v>92.31</v>
+        <v>186.89</v>
       </c>
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
@@ -3871,17 +3877,21 @@
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c r="A91" s="1"/>
-      <c r="B91" s="61"/>
-      <c r="C91" s="19" t="s">
-        <v>91</v>
+      <c r="B91" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="C91" s="64" t="s">
+        <v>118</v>
       </c>
       <c r="D91" s="61"/>
-      <c r="E91" s="60">
-        <v>186.89</v>
+      <c r="E91" s="61"/>
+      <c r="F91" s="66"/>
+      <c r="G91" s="67" t="s">
+        <v>19</v>
       </c>
-      <c r="F91" s="61"/>
-      <c r="G91" s="61"/>
-      <c r="H91" s="61"/>
+      <c r="H91" s="39">
+        <v>92.31</v>
+      </c>
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
@@ -3904,9 +3914,13 @@
     <row r="92" ht="14.25" customHeight="1">
       <c r="A92" s="1"/>
       <c r="B92" s="61"/>
-      <c r="C92" s="61"/>
+      <c r="C92" s="19" t="s">
+        <v>94</v>
+      </c>
       <c r="D92" s="61"/>
-      <c r="E92" s="61"/>
+      <c r="E92" s="60">
+        <v>186.89</v>
+      </c>
       <c r="F92" s="61"/>
       <c r="G92" s="61"/>
       <c r="H92" s="61"/>
@@ -3931,13 +3945,11 @@
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c r="A93" s="1"/>
-      <c r="B93" s="50" t="s">
-        <v>116</v>
-      </c>
+      <c r="B93" s="61"/>
       <c r="C93" s="61"/>
       <c r="D93" s="61"/>
       <c r="E93" s="61"/>
-      <c r="F93" s="63"/>
+      <c r="F93" s="61"/>
       <c r="G93" s="61"/>
       <c r="H93" s="61"/>
       <c r="I93" s="1"/>
@@ -3961,19 +3973,15 @@
     </row>
     <row r="94" ht="14.25" customHeight="1">
       <c r="A94" s="1"/>
-      <c r="B94" s="1"/>
-      <c r="C94" s="64" t="s">
-        <v>117</v>
+      <c r="B94" s="50" t="s">
+        <v>119</v>
       </c>
-      <c r="D94" s="65"/>
-      <c r="E94" s="65"/>
-      <c r="F94" s="66"/>
-      <c r="G94" s="67" t="s">
-        <v>118</v>
-      </c>
-      <c r="H94" s="39">
-        <v>186.89</v>
-      </c>
+      <c r="C94" s="61"/>
+      <c r="D94" s="61"/>
+      <c r="E94" s="61"/>
+      <c r="F94" s="63"/>
+      <c r="G94" s="61"/>
+      <c r="H94" s="61"/>
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
       <c r="K94" s="1"/>
@@ -3995,20 +4003,18 @@
     </row>
     <row r="95" ht="14.25" customHeight="1">
       <c r="A95" s="1"/>
-      <c r="B95" s="19" t="s">
-        <v>119</v>
+      <c r="B95" s="1"/>
+      <c r="C95" s="64" t="s">
+        <v>120</v>
       </c>
-      <c r="C95" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="D95" s="61"/>
-      <c r="E95" s="61"/>
+      <c r="D95" s="65"/>
+      <c r="E95" s="65"/>
       <c r="F95" s="66"/>
       <c r="G95" s="67" t="s">
-        <v>53</v>
+        <v>121</v>
       </c>
       <c r="H95" s="39">
-        <v>92.31</v>
+        <v>186.89</v>
       </c>
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
@@ -4031,17 +4037,21 @@
     </row>
     <row r="96" ht="14.25" customHeight="1">
       <c r="A96" s="1"/>
-      <c r="B96" s="61"/>
-      <c r="C96" s="19" t="s">
-        <v>91</v>
+      <c r="B96" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="C96" s="23" t="s">
+        <v>55</v>
       </c>
       <c r="D96" s="61"/>
-      <c r="E96" s="60">
-        <v>186.89</v>
+      <c r="E96" s="61"/>
+      <c r="F96" s="66"/>
+      <c r="G96" s="67" t="s">
+        <v>56</v>
       </c>
-      <c r="F96" s="61"/>
-      <c r="G96" s="61"/>
-      <c r="H96" s="61"/>
+      <c r="H96" s="39">
+        <v>92.31</v>
+      </c>
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
@@ -4063,13 +4073,17 @@
     </row>
     <row r="97" ht="14.25" customHeight="1">
       <c r="A97" s="1"/>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
+      <c r="B97" s="61"/>
+      <c r="C97" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D97" s="61"/>
+      <c r="E97" s="60">
+        <v>186.89</v>
+      </c>
+      <c r="F97" s="61"/>
+      <c r="G97" s="61"/>
+      <c r="H97" s="61"/>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
@@ -4091,15 +4105,13 @@
     </row>
     <row r="98" ht="14.25" customHeight="1">
       <c r="A98" s="1"/>
-      <c r="B98" s="50" t="s">
-        <v>120</v>
-      </c>
-      <c r="C98" s="61"/>
-      <c r="D98" s="61"/>
-      <c r="E98" s="61"/>
-      <c r="F98" s="63"/>
-      <c r="G98" s="61"/>
-      <c r="H98" s="61"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>
@@ -4121,19 +4133,15 @@
     </row>
     <row r="99" ht="14.25" customHeight="1">
       <c r="A99" s="1"/>
-      <c r="B99" s="1"/>
-      <c r="C99" s="64" t="s">
-        <v>121</v>
+      <c r="B99" s="50" t="s">
+        <v>123</v>
       </c>
-      <c r="D99" s="65"/>
-      <c r="E99" s="65"/>
-      <c r="F99" s="66"/>
-      <c r="G99" s="67" t="s">
-        <v>122</v>
-      </c>
-      <c r="H99" s="39">
-        <v>186.89</v>
-      </c>
+      <c r="C99" s="61"/>
+      <c r="D99" s="61"/>
+      <c r="E99" s="61"/>
+      <c r="F99" s="63"/>
+      <c r="G99" s="61"/>
+      <c r="H99" s="61"/>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
@@ -4155,20 +4163,18 @@
     </row>
     <row r="100" ht="14.25" customHeight="1">
       <c r="A100" s="1"/>
-      <c r="B100" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="C100" s="23" t="s">
+      <c r="B100" s="1"/>
+      <c r="C100" s="64" t="s">
         <v>124</v>
       </c>
-      <c r="D100" s="61"/>
-      <c r="E100" s="61"/>
+      <c r="D100" s="65"/>
+      <c r="E100" s="65"/>
       <c r="F100" s="66"/>
       <c r="G100" s="67" t="s">
         <v>125</v>
       </c>
       <c r="H100" s="39">
-        <v>92.31</v>
+        <v>186.89</v>
       </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
@@ -4191,17 +4197,21 @@
     </row>
     <row r="101" ht="14.25" customHeight="1">
       <c r="A101" s="1"/>
-      <c r="B101" s="61"/>
-      <c r="C101" s="19" t="s">
-        <v>91</v>
+      <c r="B101" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="C101" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="D101" s="61"/>
-      <c r="E101" s="60">
-        <v>186.89</v>
+      <c r="E101" s="61"/>
+      <c r="F101" s="66"/>
+      <c r="G101" s="67" t="s">
+        <v>128</v>
       </c>
-      <c r="F101" s="61"/>
-      <c r="G101" s="61"/>
-      <c r="H101" s="61"/>
+      <c r="H101" s="39">
+        <v>92.31</v>
+      </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
@@ -4223,13 +4233,17 @@
     </row>
     <row r="102" ht="14.25" customHeight="1">
       <c r="A102" s="1"/>
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-      <c r="H102" s="2"/>
+      <c r="B102" s="61"/>
+      <c r="C102" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D102" s="61"/>
+      <c r="E102" s="60">
+        <v>186.89</v>
+      </c>
+      <c r="F102" s="61"/>
+      <c r="G102" s="61"/>
+      <c r="H102" s="61"/>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
       <c r="K102" s="1"/>
@@ -26875,6 +26889,12 @@
     </row>
     <row r="911" ht="14.25" customHeight="1">
       <c r="A911" s="1"/>
+      <c r="B911" s="2"/>
+      <c r="C911" s="2"/>
+      <c r="D911" s="2"/>
+      <c r="E911" s="2"/>
+      <c r="F911" s="2"/>
+      <c r="G911" s="2"/>
       <c r="H911" s="2"/>
       <c r="I911" s="1"/>
       <c r="J911" s="1"/>
@@ -26897,6 +26917,8 @@
     </row>
     <row r="912" ht="14.25" customHeight="1">
       <c r="A912" s="1"/>
+      <c r="H912" s="2"/>
+      <c r="I912" s="1"/>
       <c r="J912" s="1"/>
       <c r="K912" s="1"/>
       <c r="L912" s="1"/>
@@ -26915,6 +26937,26 @@
       <c r="Y912" s="1"/>
       <c r="Z912" s="1"/>
     </row>
+    <row r="913" ht="14.25" customHeight="1">
+      <c r="A913" s="1"/>
+      <c r="J913" s="1"/>
+      <c r="K913" s="1"/>
+      <c r="L913" s="1"/>
+      <c r="M913" s="1"/>
+      <c r="N913" s="1"/>
+      <c r="O913" s="1"/>
+      <c r="P913" s="1"/>
+      <c r="Q913" s="1"/>
+      <c r="R913" s="1"/>
+      <c r="S913" s="1"/>
+      <c r="T913" s="1"/>
+      <c r="U913" s="1"/>
+      <c r="V913" s="1"/>
+      <c r="W913" s="1"/>
+      <c r="X913" s="1"/>
+      <c r="Y913" s="1"/>
+      <c r="Z913" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="C2:H2"/>
